--- a/artfynd/A 58278-2021 artfynd.xlsx
+++ b/artfynd/A 58278-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58278-2021 artfynd.xlsx
+++ b/artfynd/A 58278-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10038,6 +10038,636 @@
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>125191341</v>
+      </c>
+      <c r="B75" t="n">
+        <v>100296</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Rävamyran, Rävamyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>507222</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6894278</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>125191401</v>
+      </c>
+      <c r="B76" t="n">
+        <v>100296</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Rävamyran, Rävamyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>507214</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6894250</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>125191450</v>
+      </c>
+      <c r="B77" t="n">
+        <v>100296</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Rävamyran, Rävamyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>507204</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6894241</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>125192370</v>
+      </c>
+      <c r="B78" t="n">
+        <v>100296</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Rävamyran, Rävamyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>507268</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6894339</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>125192412</v>
+      </c>
+      <c r="B79" t="n">
+        <v>100296</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Rävamyran, Rävamyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>507266</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6894318</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58278-2021 artfynd.xlsx
+++ b/artfynd/A 58278-2021 artfynd.xlsx
@@ -10040,7 +10040,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125191341</v>
+        <v>125192412</v>
       </c>
       <c r="B75" t="n">
         <v>100296</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -10094,10 +10094,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507222</v>
+        <v>507266</v>
       </c>
       <c r="R75" t="n">
-        <v>6894278</v>
+        <v>6894318</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10166,7 +10166,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125191401</v>
+        <v>125191341</v>
       </c>
       <c r="B76" t="n">
         <v>100296</v>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507214</v>
+        <v>507222</v>
       </c>
       <c r="R76" t="n">
-        <v>6894250</v>
+        <v>6894278</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10292,7 +10292,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125191450</v>
+        <v>125192370</v>
       </c>
       <c r="B77" t="n">
         <v>100296</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507204</v>
+        <v>507268</v>
       </c>
       <c r="R77" t="n">
-        <v>6894241</v>
+        <v>6894339</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10418,7 +10418,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125192370</v>
+        <v>125191357</v>
       </c>
       <c r="B78" t="n">
         <v>100296</v>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10472,10 +10472,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507268</v>
+        <v>507214</v>
       </c>
       <c r="R78" t="n">
-        <v>6894339</v>
+        <v>6894250</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10544,7 +10544,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125192412</v>
+        <v>125191450</v>
       </c>
       <c r="B79" t="n">
         <v>100296</v>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507266</v>
+        <v>507204</v>
       </c>
       <c r="R79" t="n">
-        <v>6894318</v>
+        <v>6894241</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 58278-2021 artfynd.xlsx
+++ b/artfynd/A 58278-2021 artfynd.xlsx
@@ -10040,7 +10040,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125192412</v>
+        <v>125191450</v>
       </c>
       <c r="B75" t="n">
         <v>100296</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -10094,10 +10094,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507266</v>
+        <v>507204</v>
       </c>
       <c r="R75" t="n">
-        <v>6894318</v>
+        <v>6894241</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10292,7 +10292,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125192370</v>
+        <v>125191357</v>
       </c>
       <c r="B77" t="n">
         <v>100296</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507268</v>
+        <v>507214</v>
       </c>
       <c r="R77" t="n">
-        <v>6894339</v>
+        <v>6894250</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10418,7 +10418,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125191357</v>
+        <v>125192412</v>
       </c>
       <c r="B78" t="n">
         <v>100296</v>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -10472,10 +10472,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507214</v>
+        <v>507266</v>
       </c>
       <c r="R78" t="n">
-        <v>6894250</v>
+        <v>6894318</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10544,7 +10544,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125191450</v>
+        <v>125192370</v>
       </c>
       <c r="B79" t="n">
         <v>100296</v>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507204</v>
+        <v>507268</v>
       </c>
       <c r="R79" t="n">
-        <v>6894241</v>
+        <v>6894339</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 58278-2021 artfynd.xlsx
+++ b/artfynd/A 58278-2021 artfynd.xlsx
@@ -10040,7 +10040,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125191450</v>
+        <v>125191357</v>
       </c>
       <c r="B75" t="n">
         <v>100296</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -10094,10 +10094,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507204</v>
+        <v>507214</v>
       </c>
       <c r="R75" t="n">
-        <v>6894241</v>
+        <v>6894250</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10166,7 +10166,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125191341</v>
+        <v>125191450</v>
       </c>
       <c r="B76" t="n">
         <v>100296</v>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507222</v>
+        <v>507204</v>
       </c>
       <c r="R76" t="n">
-        <v>6894278</v>
+        <v>6894241</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10292,7 +10292,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125191357</v>
+        <v>125192412</v>
       </c>
       <c r="B77" t="n">
         <v>100296</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507214</v>
+        <v>507266</v>
       </c>
       <c r="R77" t="n">
-        <v>6894250</v>
+        <v>6894318</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10418,7 +10418,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125192412</v>
+        <v>125192370</v>
       </c>
       <c r="B78" t="n">
         <v>100296</v>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -10472,10 +10472,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507266</v>
+        <v>507268</v>
       </c>
       <c r="R78" t="n">
-        <v>6894318</v>
+        <v>6894339</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10544,7 +10544,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125192370</v>
+        <v>125191341</v>
       </c>
       <c r="B79" t="n">
         <v>100296</v>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507268</v>
+        <v>507222</v>
       </c>
       <c r="R79" t="n">
-        <v>6894339</v>
+        <v>6894278</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 58278-2021 artfynd.xlsx
+++ b/artfynd/A 58278-2021 artfynd.xlsx
@@ -10040,7 +10040,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125191357</v>
+        <v>125192412</v>
       </c>
       <c r="B75" t="n">
         <v>100296</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -10094,10 +10094,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507214</v>
+        <v>507266</v>
       </c>
       <c r="R75" t="n">
-        <v>6894250</v>
+        <v>6894318</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10166,7 +10166,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125191450</v>
+        <v>125192370</v>
       </c>
       <c r="B76" t="n">
         <v>100296</v>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507204</v>
+        <v>507268</v>
       </c>
       <c r="R76" t="n">
-        <v>6894241</v>
+        <v>6894339</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10292,7 +10292,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125192412</v>
+        <v>125191401</v>
       </c>
       <c r="B77" t="n">
         <v>100296</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507266</v>
+        <v>507214</v>
       </c>
       <c r="R77" t="n">
-        <v>6894318</v>
+        <v>6894250</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10418,7 +10418,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125192370</v>
+        <v>125191450</v>
       </c>
       <c r="B78" t="n">
         <v>100296</v>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10472,10 +10472,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507268</v>
+        <v>507204</v>
       </c>
       <c r="R78" t="n">
-        <v>6894339</v>
+        <v>6894241</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 58278-2021 artfynd.xlsx
+++ b/artfynd/A 58278-2021 artfynd.xlsx
@@ -10040,7 +10040,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125192412</v>
+        <v>125191401</v>
       </c>
       <c r="B75" t="n">
         <v>100296</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -10094,10 +10094,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>507266</v>
+        <v>507214</v>
       </c>
       <c r="R75" t="n">
-        <v>6894318</v>
+        <v>6894250</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10166,7 +10166,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125192370</v>
+        <v>125191341</v>
       </c>
       <c r="B76" t="n">
         <v>100296</v>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507268</v>
+        <v>507222</v>
       </c>
       <c r="R76" t="n">
-        <v>6894339</v>
+        <v>6894278</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10292,7 +10292,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125191401</v>
+        <v>125192412</v>
       </c>
       <c r="B77" t="n">
         <v>100296</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507214</v>
+        <v>507266</v>
       </c>
       <c r="R77" t="n">
-        <v>6894250</v>
+        <v>6894318</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10418,7 +10418,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125191450</v>
+        <v>125192370</v>
       </c>
       <c r="B78" t="n">
         <v>100296</v>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10472,10 +10472,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507204</v>
+        <v>507268</v>
       </c>
       <c r="R78" t="n">
-        <v>6894241</v>
+        <v>6894339</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10544,7 +10544,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125191341</v>
+        <v>125191450</v>
       </c>
       <c r="B79" t="n">
         <v>100296</v>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507222</v>
+        <v>507204</v>
       </c>
       <c r="R79" t="n">
-        <v>6894278</v>
+        <v>6894241</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 58278-2021 artfynd.xlsx
+++ b/artfynd/A 58278-2021 artfynd.xlsx
@@ -10040,10 +10040,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125191401</v>
+        <v>125191357</v>
       </c>
       <c r="B75" t="n">
-        <v>100296</v>
+        <v>100468</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10166,10 +10166,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125191341</v>
+        <v>125191450</v>
       </c>
       <c r="B76" t="n">
-        <v>100296</v>
+        <v>100468</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507222</v>
+        <v>507204</v>
       </c>
       <c r="R76" t="n">
-        <v>6894278</v>
+        <v>6894241</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10295,7 +10295,7 @@
         <v>125192412</v>
       </c>
       <c r="B77" t="n">
-        <v>100296</v>
+        <v>100468</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10418,10 +10418,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125192370</v>
+        <v>125191341</v>
       </c>
       <c r="B78" t="n">
-        <v>100296</v>
+        <v>100468</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10472,10 +10472,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507268</v>
+        <v>507222</v>
       </c>
       <c r="R78" t="n">
-        <v>6894339</v>
+        <v>6894278</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10544,10 +10544,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125191450</v>
+        <v>125192370</v>
       </c>
       <c r="B79" t="n">
-        <v>100296</v>
+        <v>100468</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507204</v>
+        <v>507268</v>
       </c>
       <c r="R79" t="n">
-        <v>6894241</v>
+        <v>6894339</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 58278-2021 artfynd.xlsx
+++ b/artfynd/A 58278-2021 artfynd.xlsx
@@ -10166,7 +10166,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125191450</v>
+        <v>125192370</v>
       </c>
       <c r="B76" t="n">
         <v>100468</v>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507204</v>
+        <v>507268</v>
       </c>
       <c r="R76" t="n">
-        <v>6894241</v>
+        <v>6894339</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10292,7 +10292,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125192412</v>
+        <v>125191450</v>
       </c>
       <c r="B77" t="n">
         <v>100468</v>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507266</v>
+        <v>507204</v>
       </c>
       <c r="R77" t="n">
-        <v>6894318</v>
+        <v>6894241</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10418,7 +10418,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125191341</v>
+        <v>125192412</v>
       </c>
       <c r="B78" t="n">
         <v>100468</v>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -10472,10 +10472,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>507222</v>
+        <v>507266</v>
       </c>
       <c r="R78" t="n">
-        <v>6894278</v>
+        <v>6894318</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10544,7 +10544,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125192370</v>
+        <v>125191341</v>
       </c>
       <c r="B79" t="n">
         <v>100468</v>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507268</v>
+        <v>507222</v>
       </c>
       <c r="R79" t="n">
-        <v>6894339</v>
+        <v>6894278</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 58278-2021 artfynd.xlsx
+++ b/artfynd/A 58278-2021 artfynd.xlsx
@@ -10040,15 +10040,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125191357</v>
+        <v>125191401</v>
       </c>
       <c r="B75" t="n">
-        <v>100468</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100523</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10075,7 +10070,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -10129,7 +10124,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10139,7 +10134,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10166,15 +10161,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125192370</v>
+        <v>125191450</v>
       </c>
       <c r="B76" t="n">
-        <v>100468</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100523</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10201,7 +10191,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10220,10 +10210,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>507268</v>
+        <v>507204</v>
       </c>
       <c r="R76" t="n">
-        <v>6894339</v>
+        <v>6894241</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10255,7 +10245,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10265,7 +10255,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10292,15 +10282,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125191450</v>
+        <v>125191341</v>
       </c>
       <c r="B77" t="n">
-        <v>100468</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100523</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10327,7 +10312,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10346,10 +10331,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>507204</v>
+        <v>507222</v>
       </c>
       <c r="R77" t="n">
-        <v>6894241</v>
+        <v>6894278</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10381,7 +10366,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10391,7 +10376,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10421,12 +10406,7 @@
         <v>125192412</v>
       </c>
       <c r="B78" t="n">
-        <v>100468</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100523</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10544,15 +10524,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125191341</v>
+        <v>125192370</v>
       </c>
       <c r="B79" t="n">
-        <v>100468</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100523</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10579,7 +10554,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10598,10 +10573,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>507222</v>
+        <v>507268</v>
       </c>
       <c r="R79" t="n">
-        <v>6894278</v>
+        <v>6894339</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10633,7 +10608,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10643,7 +10618,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 58278-2021 artfynd.xlsx
+++ b/artfynd/A 58278-2021 artfynd.xlsx
@@ -10043,7 +10043,7 @@
         <v>125191401</v>
       </c>
       <c r="B75" t="n">
-        <v>100523</v>
+        <v>100530</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>125191450</v>
       </c>
       <c r="B76" t="n">
-        <v>100523</v>
+        <v>100530</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>125191341</v>
       </c>
       <c r="B77" t="n">
-        <v>100523</v>
+        <v>100530</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>125192412</v>
       </c>
       <c r="B78" t="n">
-        <v>100523</v>
+        <v>100530</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>125192370</v>
       </c>
       <c r="B79" t="n">
-        <v>100523</v>
+        <v>100530</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 58278-2021 artfynd.xlsx
+++ b/artfynd/A 58278-2021 artfynd.xlsx
@@ -10043,7 +10043,7 @@
         <v>125191401</v>
       </c>
       <c r="B75" t="n">
-        <v>100530</v>
+        <v>100533</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>125191450</v>
       </c>
       <c r="B76" t="n">
-        <v>100530</v>
+        <v>100533</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>125191341</v>
       </c>
       <c r="B77" t="n">
-        <v>100530</v>
+        <v>100533</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>125192412</v>
       </c>
       <c r="B78" t="n">
-        <v>100530</v>
+        <v>100533</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>125192370</v>
       </c>
       <c r="B79" t="n">
-        <v>100530</v>
+        <v>100533</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
